--- a/data/synopses_playbill_story_nonnarrative.xlsx
+++ b/data/synopses_playbill_story_nonnarrative.xlsx
@@ -467,22 +467,32 @@
           <t>David Byrne's American Utopia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The theatrical concert includes songs from David Byrne's 
+American Utopia
+ along with songs from Talking Heads and his solo career.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://playbill.com/production/david-byrnes-american-utopiast-james-theatre-2021-2022</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SYNOPSIS (text)</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>david-byrnes-american-utopiast-james-theatre-2021-2022:nolabel | david-byrnes-american-utopia-broadway-st-james-theatre-2021:x | david-byrnes-american-utopia-broadway-st-james-theatre-2021-2:x | david-byrnes-american-utopia-broadway-st-james-theatre-2022:x | david-byrnes-american-utopia-broadway-st-james-theatre-2022-2:x</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -493,22 +503,104 @@
           <t>Freestyle Love Supreme</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Running Time:
+ 80 minutes
+concept:
+Anthony Veneziale
+Buy
+Tickets
+Buy Group
+Tickets
+                                                freestylelovesupreme.com
+                                                @freestylelove
+                                                @freestylelovesupreme
+                                                facebook.com/freestylelovesupreme
+People (45)
+Utkarsh Ambudkar
+                                        AKA UTK the INC.
+(Original)
+Andrew Bancroft
+                                        AKA Jelly Donut
+(Original)
+Aneesa Folds
+                                        AKA Young Nees
+(Original)
+Arthur Lewis
+                                        AKA Arthur the Geniuses
+(Original)
+Kaila Mullady
+                                        AKA Kaiser Rözé
+(Original)
+Chris Sullivan
+                                        AKA Shockwave
+(Original)
+Anthony Veneziale
+                                        AKA Two Touch
+(Original)
+Wayne Brady
+                                        AKA Wayne Brady [cameo at certain unannounced performances]
+(Original)
+Daveed Diggs
+                                        AKA Mr. Diggs [cameo at certain unannounced performances]
+(Original)
+Ashley Pérez Flanagan
+                                        AKA Reina Fire [cameo at certain unannounced performances]
+(Original)
+James Monroe Iglehart
+                                        AKA J-Soul [cameo at certain unannounced performances]
+(Original)
+Christopher Jackson
+                                        AKA C-Jack [cameo at certain unannounced performances]
+(Original)
+Bill Sherman
+                                        AKA King Sherman [cameo at certain unannounced performances]
+(Original)
+Lin-Manuel Miranda
+                                        AKA Lin-Man [cameo at certain unannounced performances]
+(Original)
+                                        View All Current Cast
+Utkarsh Ambudkar
+                                        AKA UTK the INC.
+(Original)
+Andrew Bancroft
+                                        AKA Jelly Donut
+(Original)
+Aneesa Folds
+                                        AKA Young Nees
+(Original)
+Arthur Lewis
+                                        AKA Arthur the Geniuses
+(Original)
+Kaila Mullady
+                                        AKA Kaiser Rözé
+(Original)
+Chris Sullivan
+                                        AKA Shockwave
+(Original)
+                                                       </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://playbill.com/production/freestyle-love-supremebooth-theatre-2019-2020</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SYNOPSIS (text)</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>freestyle-love-supremebooth-theatre-2019-2020:nolabel | freestyle-love-supreme-broadway-booth-theatre-2022:x | freestyle-love-supreme-broadway-booth-theatre-2022-2:x</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -553,22 +645,30 @@
           <t>Dancin'</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>This anthology of dance vignettes, using a wide variety of styles, existing songs and no book, is directed and choreographed by Bob Fosse.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://playbill.com/production/dancin-broadway-music-box-theatre-2023</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SYNOPSIS (text)</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>dancin-broadway-music-box-theatre-2023:nolabel | dancin-broadway-music-box-theatre:x | dancin-broadway-music-box-theatre-2:x</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/data/synopses_playbill_story_nonnarrative.xlsx
+++ b/data/synopses_playbill_story_nonnarrative.xlsx
@@ -503,104 +503,22 @@
           <t>Freestyle Love Supreme</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Running Time:
- 80 minutes
-concept:
-Anthony Veneziale
-Buy
-Tickets
-Buy Group
-Tickets
-                                                freestylelovesupreme.com
-                                                @freestylelove
-                                                @freestylelovesupreme
-                                                facebook.com/freestylelovesupreme
-People (45)
-Utkarsh Ambudkar
-                                        AKA UTK the INC.
-(Original)
-Andrew Bancroft
-                                        AKA Jelly Donut
-(Original)
-Aneesa Folds
-                                        AKA Young Nees
-(Original)
-Arthur Lewis
-                                        AKA Arthur the Geniuses
-(Original)
-Kaila Mullady
-                                        AKA Kaiser Rözé
-(Original)
-Chris Sullivan
-                                        AKA Shockwave
-(Original)
-Anthony Veneziale
-                                        AKA Two Touch
-(Original)
-Wayne Brady
-                                        AKA Wayne Brady [cameo at certain unannounced performances]
-(Original)
-Daveed Diggs
-                                        AKA Mr. Diggs [cameo at certain unannounced performances]
-(Original)
-Ashley Pérez Flanagan
-                                        AKA Reina Fire [cameo at certain unannounced performances]
-(Original)
-James Monroe Iglehart
-                                        AKA J-Soul [cameo at certain unannounced performances]
-(Original)
-Christopher Jackson
-                                        AKA C-Jack [cameo at certain unannounced performances]
-(Original)
-Bill Sherman
-                                        AKA King Sherman [cameo at certain unannounced performances]
-(Original)
-Lin-Manuel Miranda
-                                        AKA Lin-Man [cameo at certain unannounced performances]
-(Original)
-                                        View All Current Cast
-Utkarsh Ambudkar
-                                        AKA UTK the INC.
-(Original)
-Andrew Bancroft
-                                        AKA Jelly Donut
-(Original)
-Aneesa Folds
-                                        AKA Young Nees
-(Original)
-Arthur Lewis
-                                        AKA Arthur the Geniuses
-(Original)
-Kaila Mullady
-                                        AKA Kaiser Rözé
-(Original)
-Chris Sullivan
-                                        AKA Shockwave
-(Original)
-                                                       </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://playbill.com/production/freestyle-love-supremebooth-theatre-2019-2020</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SYNOPSIS (text)</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>freestyle-love-supremebooth-theatre-2019-2020:nolabel | freestyle-love-supreme-broadway-booth-theatre-2022:x | freestyle-love-supreme-broadway-booth-theatre-2022-2:x</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
